--- a/outputs/step3_disease_logistic/htn/htn_logistic_coefficients.xlsx
+++ b/outputs/step3_disease_logistic/htn/htn_logistic_coefficients.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clinic4" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clinic4_aec_best" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="clinic5_aec_best" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -453,10 +454,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.231</v>
+        <v>1.2317</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4246</v>
+        <v>3.4269</v>
       </c>
     </row>
     <row r="3">
@@ -466,10 +467,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.0006</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>2.72</v>
+        <v>2.7142</v>
       </c>
     </row>
     <row r="4">
@@ -479,10 +480,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.5236</v>
+        <v>-0.4908</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5924</v>
+        <v>0.6121</v>
       </c>
     </row>
     <row r="5">
@@ -492,10 +493,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.588</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8004</v>
+        <v>1.7577</v>
       </c>
     </row>
     <row r="6">
@@ -505,10 +506,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1.6009</v>
+        <v>-1.6057</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2017</v>
+        <v>0.2007</v>
       </c>
     </row>
   </sheetData>
@@ -549,10 +550,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9295</v>
+        <v>0.9198</v>
       </c>
       <c r="C2" t="n">
-        <v>2.5332</v>
+        <v>2.5087</v>
       </c>
     </row>
     <row r="3">
@@ -562,10 +563,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.8694</v>
       </c>
       <c r="C3" t="n">
-        <v>2.3978</v>
+        <v>2.3855</v>
       </c>
     </row>
     <row r="4">
@@ -575,10 +576,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.3721</v>
+        <v>-0.3266</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6893</v>
+        <v>0.7214</v>
       </c>
     </row>
     <row r="5">
@@ -588,10 +589,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2431</v>
+        <v>0.2016</v>
       </c>
       <c r="C5" t="n">
-        <v>1.2752</v>
+        <v>1.2234</v>
       </c>
     </row>
     <row r="6">
@@ -601,10 +602,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3741</v>
+        <v>0.3906</v>
       </c>
       <c r="C6" t="n">
-        <v>1.4537</v>
+        <v>1.4778</v>
       </c>
     </row>
     <row r="7">
@@ -614,10 +615,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.4394</v>
+        <v>-0.4553</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6444</v>
+        <v>0.6342</v>
       </c>
     </row>
     <row r="8">
@@ -627,10 +628,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0104</v>
+        <v>0.0073</v>
       </c>
       <c r="C8" t="n">
-        <v>1.0105</v>
+        <v>1.0073</v>
       </c>
     </row>
     <row r="9">
@@ -640,10 +641,158 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-1.5287</v>
+        <v>-1.5323</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2168</v>
+        <v>0.216</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>odds_ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sex_M</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7368</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2.0892</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8325</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2.299</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.3484</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.7058</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.1957</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1.2161</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>vat_sat_ratio</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.2282</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>aec_best_aec_fpca_0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.457</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>aec_best_aec_fpca_1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.3854</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6802</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>aec_best_aec_fpca_2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.0196</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-1.4694</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.2301</v>
       </c>
     </row>
   </sheetData>
